--- a/data/TTN/最新版班表/TTN_TD.xlsx
+++ b/data/TTN/最新版班表/TTN_TD.xlsx
@@ -7512,16 +7512,14 @@
 </t>
         </is>
       </c>
-      <c r="L39" s="1" t="inlineStr">
-        <is>
-          <t>
-</t>
-        </is>
-      </c>
-      <c r="M39" s="1" t="inlineStr">
-        <is>
-          <t>
-</t>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>TTN1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>TTN1</t>
         </is>
       </c>
       <c r="N39" s="1" t="inlineStr">

--- a/data/TTN/最新版班表/TTN_TD.xlsx
+++ b/data/TTN/最新版班表/TTN_TD.xlsx
@@ -934,10 +934,10 @@
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>6:00
-STD2
-14:00
-8:00</t>
+          <t>6:02
+ND0026
+14:13
+8:11</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1139,20 +1139,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>8:02
-ND0055
-16:08
-8:06</t>
-        </is>
-      </c>
-      <c r="L8" s="1" t="inlineStr">
-        <is>
-          <t>7:22
-ND0047
-15:22
-8:00</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>CMP</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>CMP</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1173,12 +1167,9 @@
 9:41</t>
         </is>
       </c>
-      <c r="P8" s="1" t="inlineStr">
-        <is>
-          <t>6:00
-STD2
-14:00
-8:00</t>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CMP</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1220,20 +1211,14 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="W8" s="1" t="inlineStr">
-        <is>
-          <t>4:42
-ND0015
-12:42
-8:00</t>
-        </is>
-      </c>
-      <c r="X8" s="1" t="inlineStr">
-        <is>
-          <t>4:00
-STD1
-13:00
-9:00</t>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>CMP</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>CMP</t>
         </is>
       </c>
       <c r="Y8" s="1" t="inlineStr">
@@ -1805,10 +1790,10 @@
       </c>
       <c r="P11" s="1" t="inlineStr">
         <is>
-          <t>4:00
-STD1
-13:00
-9:00</t>
+          <t>4:02
+ND0084
+12:23
+8:21</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1856,10 +1841,10 @@
       </c>
       <c r="W11" s="1" t="inlineStr">
         <is>
-          <t>4:00
-STD1
-13:00
-9:00</t>
+          <t>4:42
+ND0015
+12:42
+8:00</t>
         </is>
       </c>
       <c r="X11" s="1" t="inlineStr">
@@ -2032,9 +2017,9 @@
       </c>
       <c r="R12" s="1" t="inlineStr">
         <is>
-          <t>11:30
-STD3
-19:30
+          <t>13:13
+ND0513
+21:13
 8:00</t>
         </is>
       </c>
@@ -2383,12 +2368,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="M14" s="1" t="inlineStr">
-        <is>
-          <t>6:07
-ND0028
-15:33
-9:26</t>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>DTT1</t>
         </is>
       </c>
       <c r="N14" s="1" t="inlineStr">
@@ -2628,9 +2610,9 @@
       </c>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>12:30
-STD4
-20:30
+          <t>13:18
+ND0580
+21:18
 8:00</t>
         </is>
       </c>
@@ -4216,12 +4198,9 @@
 8:51</t>
         </is>
       </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>DTT1</t>
         </is>
       </c>
       <c r="L23" s="1" t="inlineStr">
@@ -4643,12 +4622,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-H9
-17:30
-8:00</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>MLP</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -5920,9 +5896,9 @@
       </c>
       <c r="T31" s="1" t="inlineStr">
         <is>
-          <t>6:00
-STD2
-14:00
+          <t>6:02
+ND0024
+14:02
 8:00</t>
         </is>
       </c>
@@ -7522,10 +7498,9 @@
           <t>TTN1</t>
         </is>
       </c>
-      <c r="N39" s="1" t="inlineStr">
-        <is>
-          <t>
-</t>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>TTN1</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
@@ -7910,18 +7885,18 @@
       </c>
       <c r="L41" s="1" t="inlineStr">
         <is>
-          <t>11:30
-STD3
-19:30
+          <t>7:22
+ND0047
+15:22
 8:00</t>
         </is>
       </c>
       <c r="M41" s="1" t="inlineStr">
         <is>
-          <t>6:57
-ND0088
-14:57
-8:00</t>
+          <t>6:07
+ND0028
+15:33
+9:26</t>
         </is>
       </c>
       <c r="N41" s="1" t="inlineStr">
@@ -8178,9 +8153,9 @@
       </c>
       <c r="T42" s="1" t="inlineStr">
         <is>
-          <t>6:02
-ND0024
-14:02
+          <t>8:30
+LUT
+17:30
 8:00</t>
         </is>
       </c>
@@ -8758,9 +8733,9 @@
       </c>
       <c r="M45" s="1" t="inlineStr">
         <is>
-          <t>6:00
-STD2
-14:00
+          <t>6:57
+ND0088
+14:57
 8:00</t>
         </is>
       </c>
@@ -9576,20 +9551,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="L49" s="1" t="inlineStr">
-        <is>
-          <t>9:32
-ND0095
-17:33
-8:01</t>
-        </is>
-      </c>
-      <c r="M49" s="1" t="inlineStr">
-        <is>
-          <t>11:17
-ND0073
-19:17
-8:00</t>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>NHS1</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -9597,36 +9566,24 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="O49" s="1" t="inlineStr">
-        <is>
-          <t>8:12
-ND0059
-17:48
-9:36</t>
-        </is>
-      </c>
-      <c r="P49" s="1" t="inlineStr">
-        <is>
-          <t>7:57
-ND0091
-16:33
-8:36</t>
-        </is>
-      </c>
-      <c r="Q49" s="1" t="inlineStr">
-        <is>
-          <t>13:18
-ND0580
-21:18
-8:00</t>
-        </is>
-      </c>
-      <c r="R49" s="1" t="inlineStr">
-        <is>
-          <t>13:13
-ND0513
-21:13
-8:00</t>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>NHS1</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>NHS1</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>NHS1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>NHS1</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -11504,10 +11461,10 @@
       </c>
       <c r="P58" s="1" t="inlineStr">
         <is>
-          <t>4:02
-ND0084
-12:23
-8:21</t>
+          <t>7:57
+ND0091
+16:33
+8:36</t>
         </is>
       </c>
       <c r="Q58" s="1" t="inlineStr">
@@ -11680,10 +11637,10 @@
       </c>
       <c r="K59" s="1" t="inlineStr">
         <is>
-          <t>6:02
-ND0026
-14:13
-8:11</t>
+          <t>8:02
+ND0055
+16:08
+8:06</t>
         </is>
       </c>
       <c r="L59" s="1" t="inlineStr">
@@ -13385,10 +13342,10 @@
       </c>
       <c r="O67" s="1" t="inlineStr">
         <is>
-          <t>16:30
-STD6
-24:30
-8:00</t>
+          <t>8:12
+ND0059
+17:48
+9:36</t>
         </is>
       </c>
       <c r="P67" s="1" t="inlineStr">
